--- a/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0002T0006Z000C1N23_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0002T0006Z000C1N23_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>62.10454809030104</v>
+        <v>10.09198906467392</v>
       </c>
       <c r="D2" t="n">
-        <v>59.35789512759421</v>
+        <v>9.645657958234059</v>
       </c>
       <c r="E2" t="n">
-        <v>12.35630615973979</v>
+        <v>2.007899750957715</v>
       </c>
       <c r="F2" t="n">
-        <v>12.35705425857188</v>
+        <v>2.008021317017931</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>40.53522792079184</v>
+        <v>6.586974537128675</v>
       </c>
       <c r="D3" t="n">
-        <v>38.57743143006426</v>
+        <v>6.268832607385442</v>
       </c>
       <c r="E3" t="n">
-        <v>12.35630615973979</v>
+        <v>2.007899750957715</v>
       </c>
       <c r="F3" t="n">
-        <v>12.35705425857188</v>
+        <v>2.008021317017931</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>23.12166232633274</v>
+        <v>3.75727012802907</v>
       </c>
       <c r="D4" t="n">
-        <v>24.05919432413396</v>
+        <v>3.909619077671768</v>
       </c>
       <c r="E4" t="n">
-        <v>12.35630615973979</v>
+        <v>2.007899750957715</v>
       </c>
       <c r="F4" t="n">
-        <v>12.35705425857188</v>
+        <v>2.008021317017931</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>34.63967740067015</v>
+        <v>5.6289475776089</v>
       </c>
       <c r="D5" t="n">
-        <v>34.1066975893837</v>
+        <v>5.542338358274852</v>
       </c>
       <c r="E5" t="n">
-        <v>12.35630615973979</v>
+        <v>2.007899750957715</v>
       </c>
       <c r="F5" t="n">
-        <v>12.35705425857188</v>
+        <v>2.008021317017931</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>25.91811229240834</v>
+        <v>4.211693247516355</v>
       </c>
       <c r="D6" t="n">
-        <v>18.39789408405705</v>
+        <v>2.989657788659271</v>
       </c>
       <c r="E6" t="n">
-        <v>12.35630615973979</v>
+        <v>2.007899750957715</v>
       </c>
       <c r="F6" t="n">
-        <v>12.35705425857188</v>
+        <v>2.008021317017931</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>31.87124807217817</v>
+        <v>5.179077811728952</v>
       </c>
       <c r="D7" t="n">
-        <v>31.72625013223361</v>
+        <v>5.155515646487961</v>
       </c>
       <c r="E7" t="n">
-        <v>12.35630615973979</v>
+        <v>2.007899750957715</v>
       </c>
       <c r="F7" t="n">
-        <v>12.35705425857188</v>
+        <v>2.008021317017931</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>26.63563232469116</v>
+        <v>4.328290252762314</v>
       </c>
       <c r="D8" t="n">
-        <v>26.12363456121625</v>
+        <v>4.24509061619764</v>
       </c>
       <c r="E8" t="n">
-        <v>12.35630615973979</v>
+        <v>2.007899750957715</v>
       </c>
       <c r="F8" t="n">
-        <v>12.35705425857188</v>
+        <v>2.008021317017931</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
